--- a/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-06).xlsx
+++ b/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-06).xlsx
@@ -912,33 +912,33 @@
   </si>
   <si>
     <t>214
-164</t>
-  </si>
-  <si>
-    <t>36</t>
-  </si>
-  <si>
-    <t>R$ 913.827,16</t>
-  </si>
-  <si>
-    <t>R$ 5.133,86
-R$ 5.294,14</t>
-  </si>
-  <si>
-    <t>(8.1%)
-(5.3%)</t>
-  </si>
-  <si>
-    <t>54.5</t>
-  </si>
-  <si>
-    <t>(11.8%)</t>
-  </si>
-  <si>
-    <t>41.5%</t>
-  </si>
-  <si>
-    <t>(14.2%)</t>
+169</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>R$ 938.120,31</t>
+  </si>
+  <si>
+    <t>R$ 5.126,34
+R$ 5.281,25</t>
+  </si>
+  <si>
+    <t>(8.4%)
+(5.7%)</t>
+  </si>
+  <si>
+    <t>54.6</t>
+  </si>
+  <si>
+    <t>(11.7%)</t>
+  </si>
+  <si>
+    <t>41.6%</t>
+  </si>
+  <si>
+    <t>(13.6%)</t>
   </si>
   <si>
     <t>3.4%</t>
@@ -947,31 +947,31 @@
     <t>0.5%</t>
   </si>
   <si>
-    <t>27.4</t>
-  </si>
-  <si>
-    <t>74.8%</t>
-  </si>
-  <si>
-    <t>10.3%</t>
-  </si>
-  <si>
-    <t>5.5</t>
-  </si>
-  <si>
-    <t>7.0</t>
-  </si>
-  <si>
-    <t>12.5</t>
+    <t>27.3</t>
+  </si>
+  <si>
+    <t>75.0%</t>
+  </si>
+  <si>
+    <t>10.0%</t>
+  </si>
+  <si>
+    <t>5.6</t>
+  </si>
+  <si>
+    <t>6.9</t>
+  </si>
+  <si>
+    <t>12.6</t>
   </si>
   <si>
     <t>19.1</t>
   </si>
   <si>
-    <t>71.6%</t>
-  </si>
-  <si>
-    <t>-R$ 25.468,02</t>
+    <t>71.8%</t>
+  </si>
+  <si>
+    <t>-R$ 26.256,62</t>
   </si>
   <si>
     <t>2.94</t>
@@ -2118,10 +2118,10 @@
         <v>0.12844036697247696</v>
       </c>
       <c r="T6" s="6">
-        <v>0.39996562396339902</v>
+        <v>0.40042470130244029</v>
       </c>
       <c r="U6" s="6">
-        <v>0.026627314945204879</v>
+        <v>0.027086392284246169</v>
       </c>
       <c r="V6" s="6">
         <v>0.028797832291255938</v>
@@ -2275,7 +2275,9 @@
       <c r="AB7" s="8">
         <v>3.1882978723404256</v>
       </c>
-      <c r="AC7" s="8"/>
+      <c r="AC7" s="8">
+        <v>19.848713</v>
+      </c>
       <c r="AD7" s="8">
         <v>27.10886595744681</v>
       </c>
@@ -2797,7 +2799,9 @@
       <c r="AB11" s="8">
         <v>6.2394174603174601</v>
       </c>
-      <c r="AC11" s="8"/>
+      <c r="AC11" s="8">
+        <v>10.865719</v>
+      </c>
       <c r="AD11" s="8">
         <v>16.665104687500001</v>
       </c>
@@ -2979,7 +2983,7 @@
         <v>19515</v>
       </c>
       <c r="B13" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C13" s="4">
         <v>44</v>
@@ -3015,25 +3019,61 @@
       <c t="s" r="N13" s="4">
         <v>52</v>
       </c>
-      <c r="O13" s="5"/>
-      <c r="P13" s="5"/>
-      <c r="Q13" s="6"/>
-      <c r="R13" s="7"/>
-      <c r="S13" s="6"/>
-      <c r="T13" s="6"/>
-      <c r="U13" s="6"/>
-      <c r="V13" s="6"/>
-      <c r="W13" s="6"/>
-      <c r="X13" s="8"/>
-      <c r="Y13" s="6"/>
-      <c r="Z13" s="6"/>
-      <c r="AA13" s="8"/>
-      <c r="AB13" s="8"/>
-      <c r="AC13" s="8"/>
-      <c r="AD13" s="8"/>
-      <c r="AE13" s="6"/>
+      <c r="O13" s="5">
+        <v>8705.6700000000001</v>
+      </c>
+      <c r="P13" s="5">
+        <v>8705.6700000000001</v>
+      </c>
+      <c r="Q13" s="6">
+        <v>-0.086103331135811034</v>
+      </c>
+      <c r="R13" s="7">
+        <v>93</v>
+      </c>
+      <c r="S13" s="6">
+        <v>-0.051020408163265252</v>
+      </c>
+      <c r="T13" s="6">
+        <v>0.27604736912839561</v>
+      </c>
+      <c r="U13" s="6">
+        <v>-0.097473566078199611</v>
+      </c>
+      <c r="V13" s="6">
+        <v>0.030625534852573091</v>
+      </c>
+      <c r="W13" s="6">
+        <v>0.028322438135146403</v>
+      </c>
+      <c r="X13" s="8">
+        <v>25.58407910447761</v>
+      </c>
+      <c r="Y13" s="6">
+        <v>0.79104477611940294</v>
+      </c>
+      <c r="Z13" s="6">
+        <v>0.029850746268656716</v>
+      </c>
+      <c r="AA13" s="8">
+        <v>7.6062500000000002</v>
+      </c>
+      <c r="AB13" s="8">
+        <v>5.6674134328358212</v>
+      </c>
+      <c r="AC13" s="8">
+        <v>13.640546000000001</v>
+      </c>
+      <c r="AD13" s="8">
+        <v>20.447264179104476</v>
+      </c>
+      <c r="AE13" s="6">
+        <v>0.76119402985074625</v>
+      </c>
       <c r="AF13" s="9"/>
-      <c r="AG13" s="5"/>
+      <c r="AG13" s="5">
+        <v>-108.3</v>
+      </c>
       <c r="AH13" s="10">
         <v>5</v>
       </c>
@@ -4819,7 +4859,9 @@
       <c r="AB27" s="8">
         <v>5.7083343749999997</v>
       </c>
-      <c r="AC27" s="8"/>
+      <c r="AC27" s="8">
+        <v>14.475519999999999</v>
+      </c>
       <c r="AD27" s="8">
         <v>22.403646875</v>
       </c>
@@ -4948,7 +4990,9 @@
       <c r="AB28" s="8">
         <v>8.4823242424242427</v>
       </c>
-      <c r="AC28" s="8"/>
+      <c r="AC28" s="8">
+        <v>11.834282999999999</v>
+      </c>
       <c r="AD28" s="8">
         <v>18.812121212121212</v>
       </c>
@@ -5880,7 +5924,7 @@
         <v>19562</v>
       </c>
       <c r="B36" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C36" s="4">
         <v>44</v>
@@ -5916,25 +5960,59 @@
       <c t="s" r="N36" s="4">
         <v>52</v>
       </c>
-      <c r="O36" s="5"/>
-      <c r="P36" s="5"/>
-      <c r="Q36" s="6"/>
-      <c r="R36" s="7"/>
-      <c r="S36" s="6"/>
-      <c r="T36" s="6"/>
-      <c r="U36" s="6"/>
-      <c r="V36" s="6"/>
-      <c r="W36" s="6"/>
-      <c r="X36" s="8"/>
-      <c r="Y36" s="6"/>
-      <c r="Z36" s="6"/>
-      <c r="AA36" s="8"/>
-      <c r="AB36" s="8"/>
+      <c r="O36" s="5">
+        <v>4582.8500000000004</v>
+      </c>
+      <c r="P36" s="5">
+        <v>4582.8500000000004</v>
+      </c>
+      <c r="Q36" s="6">
+        <v>0.29800039652193644</v>
+      </c>
+      <c r="R36" s="7">
+        <v>56</v>
+      </c>
+      <c r="S36" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="T36" s="6">
+        <v>0.33444605431118191</v>
+      </c>
+      <c r="U36" s="6">
+        <v>-0.00047217342919798812</v>
+      </c>
+      <c r="V36" s="6">
+        <v>0.054182441057420594</v>
+      </c>
+      <c r="W36" s="6">
+        <v>0.011309556280480486</v>
+      </c>
+      <c r="X36" s="8">
+        <v>27.120000000000001</v>
+      </c>
+      <c r="Y36" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z36" s="6">
+        <v>0.033333333333333333</v>
+      </c>
+      <c r="AA36" s="8">
+        <v>6.5070000000000006</v>
+      </c>
+      <c r="AB36" s="8">
+        <v>4.503333333333333</v>
+      </c>
       <c r="AC36" s="8"/>
-      <c r="AD36" s="8"/>
-      <c r="AE36" s="6"/>
+      <c r="AD36" s="8">
+        <v>18.731110000000001</v>
+      </c>
+      <c r="AE36" s="6">
+        <v>0.80000000000000004</v>
+      </c>
       <c r="AF36" s="9"/>
-      <c r="AG36" s="5"/>
+      <c r="AG36" s="5">
+        <v>0</v>
+      </c>
       <c r="AH36" s="10">
         <v>4</v>
       </c>
@@ -6315,7 +6393,9 @@
       <c r="AB39" s="8">
         <v>2.3197937500000001</v>
       </c>
-      <c r="AC39" s="8"/>
+      <c r="AC39" s="8">
+        <v>4.3714029999999999</v>
+      </c>
       <c r="AD39" s="8">
         <v>9.0922233333333331</v>
       </c>
@@ -6628,7 +6708,7 @@
         <v>19579</v>
       </c>
       <c r="B42" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C42" s="4">
         <v>44</v>
@@ -6664,25 +6744,61 @@
       <c t="s" r="N42" s="4">
         <v>52</v>
       </c>
-      <c r="O42" s="5"/>
-      <c r="P42" s="5"/>
-      <c r="Q42" s="6"/>
-      <c r="R42" s="7"/>
-      <c r="S42" s="6"/>
-      <c r="T42" s="6"/>
-      <c r="U42" s="6"/>
-      <c r="V42" s="6"/>
-      <c r="W42" s="6"/>
-      <c r="X42" s="8"/>
-      <c r="Y42" s="6"/>
-      <c r="Z42" s="6"/>
-      <c r="AA42" s="8"/>
-      <c r="AB42" s="8"/>
-      <c r="AC42" s="8"/>
-      <c r="AD42" s="8"/>
-      <c r="AE42" s="6"/>
+      <c r="O42" s="5">
+        <v>3381.8299999999999</v>
+      </c>
+      <c r="P42" s="5">
+        <v>3381.8299999999999</v>
+      </c>
+      <c r="Q42" s="6">
+        <v>-0.23470521544515821</v>
+      </c>
+      <c r="R42" s="7">
+        <v>40</v>
+      </c>
+      <c r="S42" s="6">
+        <v>-0.13043478260869568</v>
+      </c>
+      <c r="T42" s="6">
+        <v>0.40581430763817222</v>
+      </c>
+      <c r="U42" s="6">
+        <v>0.029074495169774946</v>
+      </c>
+      <c r="V42" s="6">
+        <v>0.08154238977121854</v>
+      </c>
+      <c r="W42" s="6">
+        <v>0.019898250355576717</v>
+      </c>
+      <c r="X42" s="8">
+        <v>23.942776666666667</v>
+      </c>
+      <c r="Y42" s="6">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="Z42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA42" s="8">
+        <v>6.0788609756097562</v>
+      </c>
+      <c r="AB42" s="8">
+        <v>4.1600000000000001</v>
+      </c>
+      <c r="AC42" s="8">
+        <v>10.459462</v>
+      </c>
+      <c r="AD42" s="8">
+        <v>17.238890000000001</v>
+      </c>
+      <c r="AE42" s="6">
+        <v>0.80000000000000004</v>
+      </c>
       <c r="AF42" s="9"/>
-      <c r="AG42" s="5"/>
+      <c r="AG42" s="5">
+        <v>0</v>
+      </c>
       <c r="AH42" s="10">
         <v>3</v>
       </c>
@@ -6932,7 +7048,9 @@
       <c r="AB44" s="8">
         <v>4.7959341463414633</v>
       </c>
-      <c r="AC44" s="8"/>
+      <c r="AC44" s="8">
+        <v>7.7656299999999998</v>
+      </c>
       <c r="AD44" s="8">
         <v>15.134470454545454</v>
       </c>
@@ -7431,7 +7549,7 @@
         <v>0.028033212174375575</v>
       </c>
       <c r="W48" s="6">
-        <v>0.0098397715554850475</v>
+        <v>0.0092266667910917838</v>
       </c>
       <c r="X48" s="8">
         <v>35.787209302325579</v>
@@ -7708,7 +7826,9 @@
       <c r="AB50" s="8">
         <v>3.043135294117647</v>
       </c>
-      <c r="AC50" s="8"/>
+      <c r="AC50" s="8">
+        <v>6.314705</v>
+      </c>
       <c r="AD50" s="8">
         <v>14.260782352941177</v>
       </c>
@@ -8323,7 +8443,9 @@
       <c r="AB55" s="8">
         <v>20.942647058823528</v>
       </c>
-      <c r="AC55" s="8"/>
+      <c r="AC55" s="8">
+        <v>23.145026999999999</v>
+      </c>
       <c r="AD55" s="8">
         <v>30.015197058823532</v>
       </c>
@@ -9196,7 +9318,9 @@
       <c r="AB62" s="8">
         <v>4.0212136363636368</v>
       </c>
-      <c r="AC62" s="8"/>
+      <c r="AC62" s="8">
+        <v>7.7719690000000003</v>
+      </c>
       <c r="AD62" s="8">
         <v>14.715909090909092</v>
       </c>
@@ -10323,7 +10447,9 @@
       <c r="AB71" s="8">
         <v>6.1666653846153849</v>
       </c>
-      <c r="AC71" s="8"/>
+      <c r="AC71" s="8">
+        <v>9.6850559999999994</v>
+      </c>
       <c r="AD71" s="8">
         <v>16.427586206896549</v>
       </c>
@@ -10801,7 +10927,9 @@
       <c r="AB75" s="8">
         <v>7.9114052631578948</v>
       </c>
-      <c r="AC75" s="8"/>
+      <c r="AC75" s="8">
+        <v>12.829824</v>
+      </c>
       <c r="AD75" s="8">
         <v>19.762278947368419</v>
       </c>
@@ -11420,10 +11548,10 @@
         <v>-0.18309859154929575</v>
       </c>
       <c r="T80" s="6">
-        <v>0.28354589730552482</v>
+        <v>0.36827492115704991</v>
       </c>
       <c r="U80" s="6">
-        <v>-0.056422941540956638</v>
+        <v>0.027897357841542427</v>
       </c>
       <c r="V80" s="6">
         <v>0.032423703403366907</v>
@@ -12729,7 +12857,7 @@
         <v>19698</v>
       </c>
       <c r="B91" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C91" s="4">
         <v>44</v>
@@ -12765,25 +12893,61 @@
       <c t="s" r="N91" s="4">
         <v>52</v>
       </c>
-      <c r="O91" s="5"/>
-      <c r="P91" s="5"/>
-      <c r="Q91" s="6"/>
-      <c r="R91" s="7"/>
-      <c r="S91" s="6"/>
-      <c r="T91" s="6"/>
-      <c r="U91" s="6"/>
-      <c r="V91" s="6"/>
-      <c r="W91" s="6"/>
-      <c r="X91" s="8"/>
-      <c r="Y91" s="6"/>
-      <c r="Z91" s="6"/>
-      <c r="AA91" s="8"/>
-      <c r="AB91" s="8"/>
-      <c r="AC91" s="8"/>
-      <c r="AD91" s="8"/>
-      <c r="AE91" s="6"/>
+      <c r="O91" s="5">
+        <v>4718.1999999999998</v>
+      </c>
+      <c r="P91" s="5">
+        <v>4718.1999999999998</v>
+      </c>
+      <c r="Q91" s="6">
+        <v>-0.48264783605083394</v>
+      </c>
+      <c r="R91" s="7">
+        <v>52</v>
+      </c>
+      <c r="S91" s="6">
+        <v>-0.34999999999999998</v>
+      </c>
+      <c r="T91" s="6">
+        <v>0.99869939807553731</v>
+      </c>
+      <c r="U91" s="6">
+        <v>0.66460800729091596</v>
+      </c>
+      <c r="V91" s="6">
+        <v>0.044745135856894581</v>
+      </c>
+      <c r="W91" s="6">
+        <v>0.020225191810436183</v>
+      </c>
+      <c r="X91" s="8">
+        <v>26.042776666666668</v>
+      </c>
+      <c r="Y91" s="6">
+        <v>0.59999999999999998</v>
+      </c>
+      <c r="Z91" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA91" s="8">
+        <v>6.7411943396226413</v>
+      </c>
+      <c r="AB91" s="8">
+        <v>5.8605566666666666</v>
+      </c>
+      <c r="AC91" s="8">
+        <v>11.534443</v>
+      </c>
+      <c r="AD91" s="8">
+        <v>18.496109999999998</v>
+      </c>
+      <c r="AE91" s="6">
+        <v>0.80000000000000004</v>
+      </c>
       <c r="AF91" s="9"/>
-      <c r="AG91" s="5"/>
+      <c r="AG91" s="5">
+        <v>0</v>
+      </c>
       <c r="AH91" s="10">
         <v>2</v>
       </c>
@@ -13005,10 +13169,10 @@
         <v>0.36734693877551017</v>
       </c>
       <c r="T93" s="6">
-        <v>0.36066968047183878</v>
+        <v>0.38070581372739648</v>
       </c>
       <c r="U93" s="6">
-        <v>0.018518176449831125</v>
+        <v>0.038554309705388846</v>
       </c>
       <c r="V93" s="6">
         <v>0.067768217858145921</v>
@@ -19122,7 +19286,9 @@
       <c r="AB142" s="8">
         <v>10.369751851851852</v>
       </c>
-      <c r="AC142" s="8"/>
+      <c r="AC142" s="8">
+        <v>16.896296</v>
+      </c>
       <c r="AD142" s="8">
         <v>25.716666666666669</v>
       </c>
@@ -21383,7 +21549,7 @@
         <v>19868</v>
       </c>
       <c r="B161" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C161" s="4">
         <v>44</v>
@@ -21419,25 +21585,57 @@
       <c t="s" r="N161" s="4">
         <v>52</v>
       </c>
-      <c r="O161" s="5"/>
-      <c r="P161" s="5"/>
-      <c r="Q161" s="6"/>
-      <c r="R161" s="7"/>
-      <c r="S161" s="6"/>
-      <c r="T161" s="6"/>
-      <c r="U161" s="6"/>
-      <c r="V161" s="6"/>
-      <c r="W161" s="6"/>
-      <c r="X161" s="8"/>
-      <c r="Y161" s="6"/>
-      <c r="Z161" s="6"/>
-      <c r="AA161" s="8"/>
+      <c r="O161" s="5">
+        <v>2904.5999999999999</v>
+      </c>
+      <c r="P161" s="5">
+        <v>2904.5999999999999</v>
+      </c>
+      <c r="Q161" s="6">
+        <v>-0.052240023493327237</v>
+      </c>
+      <c r="R161" s="7">
+        <v>37</v>
+      </c>
+      <c r="S161" s="6">
+        <v>-0.13953488372093026</v>
+      </c>
+      <c r="T161" s="6">
+        <v>-0.15142566962748744</v>
+      </c>
+      <c r="U161" s="6">
+        <v>-0.50180093644563795</v>
+      </c>
+      <c r="V161" s="6">
+        <v>0.043480685808717209</v>
+      </c>
+      <c r="W161" s="6">
+        <v>-0.0096453900709219855</v>
+      </c>
+      <c r="X161" s="8">
+        <v>6.4500000000000002</v>
+      </c>
+      <c r="Y161" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z161" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA161" s="8">
+        <v>21.448611111111109</v>
+      </c>
       <c r="AB161" s="8"/>
       <c r="AC161" s="8"/>
-      <c r="AD161" s="8"/>
-      <c r="AE161" s="6"/>
+      <c r="AD161" s="8">
+        <v>1.3667</v>
+      </c>
+      <c r="AE161" s="6">
+        <v>1</v>
+      </c>
       <c r="AF161" s="9"/>
-      <c r="AG161" s="5"/>
+      <c r="AG161" s="5">
+        <v>-680.29999999999995</v>
+      </c>
       <c r="AH161" s="10">
         <v>5</v>
       </c>
@@ -21556,7 +21754,9 @@
       <c r="AB162" s="8">
         <v>2.1283962962962963</v>
       </c>
-      <c r="AC162" s="8"/>
+      <c r="AC162" s="8">
+        <v>9.5006170000000001</v>
+      </c>
       <c r="AD162" s="8">
         <v>17.445677777777778</v>
       </c>
@@ -23221,7 +23421,9 @@
       <c r="AB175" s="8">
         <v>3.6813705882352941</v>
       </c>
-      <c r="AC175" s="8"/>
+      <c r="AC175" s="8">
+        <v>9.9892149999999997</v>
+      </c>
       <c r="AD175" s="8">
         <v>16.946076470588235</v>
       </c>
@@ -23864,7 +24066,9 @@
       <c r="AB180" s="8">
         <v>10.488888888888889</v>
       </c>
-      <c r="AC180" s="8"/>
+      <c r="AC180" s="8">
+        <v>15.613887999999999</v>
+      </c>
       <c r="AD180" s="8">
         <v>22.531477777777777</v>
       </c>
@@ -23993,7 +24197,9 @@
       <c r="AB181" s="8">
         <v>1.0305500000000001</v>
       </c>
-      <c r="AC181" s="8"/>
+      <c r="AC181" s="8">
+        <v>4.4687489999999999</v>
+      </c>
       <c r="AD181" s="8">
         <v>9.9701374999999999</v>
       </c>
@@ -24227,10 +24433,10 @@
         <v>0.29545454545454541</v>
       </c>
       <c r="T183" s="6">
-        <v>5.5357089235911836</v>
+        <v>5.7027720824397656</v>
       </c>
       <c r="U183" s="6">
-        <v>0.39291535526223054</v>
+        <v>0.55997851411081245</v>
       </c>
       <c r="V183" s="6">
         <v>0.023076287995489372</v>
@@ -24722,7 +24928,7 @@
         <v>0.17551640820629968</v>
       </c>
       <c r="W187" s="6">
-        <v>0.074598251548565642</v>
+        <v>0.097705926283881722</v>
       </c>
       <c r="X187" s="8">
         <v>52.108337499999998</v>
@@ -24739,7 +24945,9 @@
       <c r="AB187" s="8">
         <v>18.3791625</v>
       </c>
-      <c r="AC187" s="8"/>
+      <c r="AC187" s="8">
+        <v>31.068749</v>
+      </c>
       <c r="AD187" s="8">
         <v>38.018749999999997</v>
       </c>
@@ -25001,7 +25209,9 @@
       <c r="AB189" s="8">
         <v>16.509782608695652</v>
       </c>
-      <c r="AC189" s="8"/>
+      <c r="AC189" s="8">
+        <v>19.809186</v>
+      </c>
       <c r="AD189" s="8">
         <v>22.86994107142857</v>
       </c>
@@ -25130,7 +25340,9 @@
       <c r="AB190" s="8">
         <v>6.3103190476190472</v>
       </c>
-      <c r="AC190" s="8"/>
+      <c r="AC190" s="8">
+        <v>11.415077999999999</v>
+      </c>
       <c r="AD190" s="8">
         <v>18.368252380952381</v>
       </c>
@@ -25388,7 +25600,9 @@
       <c r="AB192" s="8">
         <v>16.872225</v>
       </c>
-      <c r="AC192" s="8"/>
+      <c r="AC192" s="8">
+        <v>22.805554999999998</v>
+      </c>
       <c r="AD192" s="8">
         <v>30.131941666666666</v>
       </c>
@@ -25779,7 +25993,9 @@
       <c r="AB195" s="8">
         <v>4.7698428571428577</v>
       </c>
-      <c r="AC195" s="8"/>
+      <c r="AC195" s="8">
+        <v>9.0317450000000008</v>
+      </c>
       <c r="AD195" s="8">
         <v>15.968252380952382</v>
       </c>
@@ -26301,7 +26517,9 @@
       <c r="AB199" s="8">
         <v>7.1083299999999996</v>
       </c>
-      <c r="AC199" s="8"/>
+      <c r="AC199" s="8">
+        <v>10.978028999999999</v>
+      </c>
       <c r="AD199" s="8">
         <v>17.065154545454547</v>
       </c>
@@ -26430,7 +26648,9 @@
       <c r="AB200" s="8">
         <v>4.8645874999999998</v>
       </c>
-      <c r="AC200" s="8"/>
+      <c r="AC200" s="8">
+        <v>9.4571749999999994</v>
+      </c>
       <c r="AD200" s="8">
         <v>16.043749999999999</v>
       </c>
@@ -27130,7 +27350,9 @@
       <c r="AB206" s="8">
         <v>6.5299999999999994</v>
       </c>
-      <c r="AC206" s="8"/>
+      <c r="AC206" s="8">
+        <v>19.786666</v>
+      </c>
       <c r="AD206" s="8">
         <v>26.74334</v>
       </c>

--- a/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-06).xlsx
+++ b/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-06).xlsx
@@ -912,33 +912,33 @@
   </si>
   <si>
     <t>214
-169</t>
-  </si>
-  <si>
-    <t>31</t>
-  </si>
-  <si>
-    <t>R$ 938.120,31</t>
-  </si>
-  <si>
-    <t>R$ 5.126,34
-R$ 5.281,25</t>
-  </si>
-  <si>
-    <t>(8.4%)
-(5.7%)</t>
-  </si>
-  <si>
-    <t>54.6</t>
-  </si>
-  <si>
-    <t>(11.7%)</t>
-  </si>
-  <si>
-    <t>41.6%</t>
-  </si>
-  <si>
-    <t>(13.6%)</t>
+170</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>R$ 940.974,73</t>
+  </si>
+  <si>
+    <t>R$ 5.113,99
+R$ 5.266,98</t>
+  </si>
+  <si>
+    <t>(8.6%)
+(5.9%)</t>
+  </si>
+  <si>
+    <t>54.4</t>
+  </si>
+  <si>
+    <t>(11.8%)</t>
+  </si>
+  <si>
+    <t>41.5%</t>
+  </si>
+  <si>
+    <t>(13.7%)</t>
   </si>
   <si>
     <t>3.4%</t>
@@ -947,28 +947,28 @@
     <t>0.5%</t>
   </si>
   <si>
-    <t>27.3</t>
-  </si>
-  <si>
-    <t>75.0%</t>
-  </si>
-  <si>
-    <t>10.0%</t>
+    <t>27.4</t>
+  </si>
+  <si>
+    <t>74.8%</t>
+  </si>
+  <si>
+    <t>10.2%</t>
   </si>
   <si>
     <t>5.6</t>
   </si>
   <si>
-    <t>6.9</t>
-  </si>
-  <si>
-    <t>12.6</t>
-  </si>
-  <si>
-    <t>19.1</t>
-  </si>
-  <si>
-    <t>71.8%</t>
+    <t>7.0</t>
+  </si>
+  <si>
+    <t>12.7</t>
+  </si>
+  <si>
+    <t>19.2</t>
+  </si>
+  <si>
+    <t>71.6%</t>
   </si>
   <si>
     <t>-R$ 26.256,62</t>
@@ -6002,7 +6002,9 @@
       <c r="AB36" s="8">
         <v>4.503333333333333</v>
       </c>
-      <c r="AC36" s="8"/>
+      <c r="AC36" s="8">
+        <v>11.779999</v>
+      </c>
       <c r="AD36" s="8">
         <v>18.731110000000001</v>
       </c>
@@ -14254,7 +14256,7 @@
         <v>19719</v>
       </c>
       <c r="B102" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C102" s="4">
         <v>44</v>
@@ -14290,25 +14292,61 @@
       <c t="s" r="N102" s="4">
         <v>52</v>
       </c>
-      <c r="O102" s="5"/>
-      <c r="P102" s="5"/>
-      <c r="Q102" s="6"/>
-      <c r="R102" s="7"/>
-      <c r="S102" s="6"/>
-      <c r="T102" s="6"/>
-      <c r="U102" s="6"/>
-      <c r="V102" s="6"/>
-      <c r="W102" s="6"/>
-      <c r="X102" s="8"/>
-      <c r="Y102" s="6"/>
-      <c r="Z102" s="6"/>
-      <c r="AA102" s="8"/>
-      <c r="AB102" s="8"/>
-      <c r="AC102" s="8"/>
-      <c r="AD102" s="8"/>
-      <c r="AE102" s="6"/>
+      <c r="O102" s="5">
+        <v>2854.4200000000001</v>
+      </c>
+      <c r="P102" s="5">
+        <v>2854.4200000000001</v>
+      </c>
+      <c r="Q102" s="6">
+        <v>-0.42335881440299949</v>
+      </c>
+      <c r="R102" s="7">
+        <v>31</v>
+      </c>
+      <c r="S102" s="6">
+        <v>-0.34042553191489366</v>
+      </c>
+      <c r="T102" s="6">
+        <v>0</v>
+      </c>
+      <c r="U102" s="6">
+        <v>-0.37368362049032733</v>
+      </c>
+      <c r="V102" s="6">
+        <v>0.016241653295590699</v>
+      </c>
+      <c r="W102" s="6">
+        <v>-0.01026110383195185</v>
+      </c>
+      <c r="X102" s="8">
+        <v>61.634374999999999</v>
+      </c>
+      <c r="Y102" s="6">
+        <v>0.25</v>
+      </c>
+      <c r="Z102" s="6">
+        <v>0.8125</v>
+      </c>
+      <c r="AA102" s="8">
+        <v>6.0130218749999997</v>
+      </c>
+      <c r="AB102" s="8">
+        <v>29.359999999999999</v>
+      </c>
+      <c r="AC102" s="8">
+        <v>34.974583000000003</v>
+      </c>
+      <c r="AD102" s="8">
+        <v>39.402081250000002</v>
+      </c>
+      <c r="AE102" s="6">
+        <v>0.0625</v>
+      </c>
       <c r="AF102" s="9"/>
-      <c r="AG102" s="5"/>
+      <c r="AG102" s="5">
+        <v>0</v>
+      </c>
       <c r="AH102" s="10">
         <v>2</v>
       </c>
@@ -20807,7 +20845,7 @@
         <v>0.017378651438611902</v>
       </c>
       <c r="W154" s="6">
-        <v>-0.024961386678758423</v>
+        <v>-0.020302990584017626</v>
       </c>
       <c r="X154" s="8">
         <v>27.247438461538461</v>

--- a/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-06).xlsx
+++ b/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-06).xlsx
@@ -911,37 +911,40 @@
     <t>GUIMARAES FRAGA,MARESSA</t>
   </si>
   <si>
-    <t>214
-170</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>R$ 940.974,73</t>
-  </si>
-  <si>
-    <t>R$ 5.113,99
-R$ 5.266,98</t>
-  </si>
-  <si>
-    <t>(8.6%)
-(5.9%)</t>
-  </si>
-  <si>
-    <t>54.4</t>
+    <t>DE LOURDES RAMOS,MARIA</t>
+  </si>
+  <si>
+    <t>215
+172</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>R$ 953.021,83</t>
+  </si>
+  <si>
+    <t>R$ 5.123,77
+R$ 5.275,77</t>
+  </si>
+  <si>
+    <t>(8.5%)
+(5.8%)</t>
+  </si>
+  <si>
+    <t>54.5</t>
   </si>
   <si>
     <t>(11.8%)</t>
   </si>
   <si>
-    <t>41.5%</t>
-  </si>
-  <si>
-    <t>(13.7%)</t>
-  </si>
-  <si>
-    <t>3.4%</t>
+    <t>35.0%</t>
+  </si>
+  <si>
+    <t>(19.9%)</t>
+  </si>
+  <si>
+    <t>3.5%</t>
   </si>
   <si>
     <t>0.5%</t>
@@ -950,7 +953,7 @@
     <t>27.4</t>
   </si>
   <si>
-    <t>74.8%</t>
+    <t>75.0%</t>
   </si>
   <si>
     <t>10.2%</t>
@@ -959,7 +962,7 @@
     <t>5.6</t>
   </si>
   <si>
-    <t>7.0</t>
+    <t>6.9</t>
   </si>
   <si>
     <t>12.7</t>
@@ -968,10 +971,10 @@
     <t>19.2</t>
   </si>
   <si>
-    <t>71.6%</t>
-  </si>
-  <si>
-    <t>-R$ 26.256,62</t>
+    <t>71.7%</t>
+  </si>
+  <si>
+    <t>-R$ 26.308,52</t>
   </si>
   <si>
     <t>2.94</t>
@@ -2249,10 +2252,10 @@
         <v>0.29230769230769238</v>
       </c>
       <c r="T7" s="6">
-        <v>0.53601507029432593</v>
+        <v>0.55072392029938311</v>
       </c>
       <c r="U7" s="6">
-        <v>0.3059523616870638</v>
+        <v>0.32066121169212097</v>
       </c>
       <c r="V7" s="6">
         <v>0.023400222514412865</v>
@@ -5694,7 +5697,7 @@
         <v>19560</v>
       </c>
       <c r="B34" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C34" s="4">
         <v>44</v>
@@ -5730,25 +5733,61 @@
       <c t="s" r="N34" s="4">
         <v>52</v>
       </c>
-      <c r="O34" s="5"/>
-      <c r="P34" s="5"/>
-      <c r="Q34" s="6"/>
-      <c r="R34" s="7"/>
-      <c r="S34" s="6"/>
-      <c r="T34" s="6"/>
-      <c r="U34" s="6"/>
-      <c r="V34" s="6"/>
-      <c r="W34" s="6"/>
-      <c r="X34" s="8"/>
-      <c r="Y34" s="6"/>
-      <c r="Z34" s="6"/>
-      <c r="AA34" s="8"/>
-      <c r="AB34" s="8"/>
-      <c r="AC34" s="8"/>
-      <c r="AD34" s="8"/>
-      <c r="AE34" s="6"/>
+      <c r="O34" s="5">
+        <v>9726.3999999999996</v>
+      </c>
+      <c r="P34" s="5">
+        <v>9726.3999999999996</v>
+      </c>
+      <c r="Q34" s="6">
+        <v>-0.043126406204960888</v>
+      </c>
+      <c r="R34" s="7">
+        <v>94</v>
+      </c>
+      <c r="S34" s="6">
+        <v>-0.16814159292035402</v>
+      </c>
+      <c r="T34" s="6">
+        <v>-5.8675985976311891</v>
+      </c>
+      <c r="U34" s="6">
+        <v>-6.237235873498931</v>
+      </c>
+      <c r="V34" s="6">
+        <v>0.055186451307780882</v>
+      </c>
+      <c r="W34" s="6">
+        <v>0.027483498519493336</v>
+      </c>
+      <c r="X34" s="8">
+        <v>27.071896078431372</v>
+      </c>
+      <c r="Y34" s="6">
+        <v>0.92307692307692313</v>
+      </c>
+      <c r="Z34" s="6">
+        <v>0.13725490196078433</v>
+      </c>
+      <c r="AA34" s="8">
+        <v>11.513586956521738</v>
+      </c>
+      <c r="AB34" s="8">
+        <v>3.7269999999999999</v>
+      </c>
+      <c r="AC34" s="8">
+        <v>15.057065</v>
+      </c>
+      <c r="AD34" s="8">
+        <v>20.89248431372549</v>
+      </c>
+      <c r="AE34" s="6">
+        <v>0.80392156862745101</v>
+      </c>
       <c r="AF34" s="9"/>
-      <c r="AG34" s="5"/>
+      <c r="AG34" s="5">
+        <v>-51.899999999999999</v>
+      </c>
       <c r="AH34" s="10">
         <v>4</v>
       </c>
@@ -16014,7 +16053,9 @@
       <c r="Z116" s="6"/>
       <c r="AA116" s="8"/>
       <c r="AB116" s="8"/>
-      <c r="AC116" s="8"/>
+      <c r="AC116" s="8">
+        <v>10.067036999999999</v>
+      </c>
       <c r="AD116" s="8"/>
       <c r="AE116" s="6"/>
       <c r="AF116" s="9"/>
@@ -19151,7 +19192,7 @@
         <v>19793</v>
       </c>
       <c r="B141" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C141" s="4">
         <v>44</v>
@@ -19187,25 +19228,61 @@
       <c t="s" r="N141" s="4">
         <v>52</v>
       </c>
-      <c r="O141" s="5"/>
-      <c r="P141" s="5"/>
-      <c r="Q141" s="6"/>
-      <c r="R141" s="7"/>
-      <c r="S141" s="6"/>
-      <c r="T141" s="6"/>
-      <c r="U141" s="6"/>
-      <c r="V141" s="6"/>
-      <c r="W141" s="6"/>
-      <c r="X141" s="8"/>
-      <c r="Y141" s="6"/>
-      <c r="Z141" s="6"/>
-      <c r="AA141" s="8"/>
-      <c r="AB141" s="8"/>
-      <c r="AC141" s="8"/>
-      <c r="AD141" s="8"/>
-      <c r="AE141" s="6"/>
+      <c r="O141" s="5">
+        <v>2320.6999999999998</v>
+      </c>
+      <c r="P141" s="5">
+        <v>2320.6999999999998</v>
+      </c>
+      <c r="Q141" s="6">
+        <v>0.14144201305376414</v>
+      </c>
+      <c r="R141" s="7">
+        <v>24</v>
+      </c>
+      <c r="S141" s="6">
+        <v>-0.1428571428571429</v>
+      </c>
+      <c r="T141" s="6">
+        <v>0.324320205110527</v>
+      </c>
+      <c r="U141" s="6">
+        <v>-0.044482311371568925</v>
+      </c>
+      <c r="V141" s="6">
+        <v>0.17481751195759901</v>
+      </c>
+      <c r="W141" s="6">
+        <v>0.085960701512474688</v>
+      </c>
+      <c r="X141" s="8">
+        <v>24.339390909090909</v>
+      </c>
+      <c r="Y141" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z141" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA141" s="8">
+        <v>4.2909708333333336</v>
+      </c>
+      <c r="AB141" s="8">
+        <v>2.4772727272727271</v>
+      </c>
+      <c r="AC141" s="8">
+        <v>7.8242409999999998</v>
+      </c>
+      <c r="AD141" s="8">
+        <v>15.7697</v>
+      </c>
+      <c r="AE141" s="6">
+        <v>0.81818181818181823</v>
+      </c>
       <c r="AF141" s="9"/>
-      <c r="AG141" s="5"/>
+      <c r="AG141" s="5">
+        <v>0</v>
+      </c>
       <c r="AH141" s="10">
         <v>4</v>
       </c>
@@ -28367,112 +28444,203 @@
         <v>56</v>
       </c>
     </row>
-    <row r="216" ht="24.75" customHeight="1">
-      <c t="s" r="A216" s="14">
+    <row r="216" ht="13.5" customHeight="1">
+      <c r="A216" s="2">
+        <v>19980</v>
+      </c>
+      <c r="B216" s="3">
+        <v>-1</v>
+      </c>
+      <c t="s" r="C216" s="4">
+        <v>44</v>
+      </c>
+      <c t="s" r="D216" s="4">
+        <v>45</v>
+      </c>
+      <c t="s" r="E216" s="4">
+        <v>46</v>
+      </c>
+      <c t="s" r="F216" s="4">
+        <v>47</v>
+      </c>
+      <c t="s" r="G216" s="4">
+        <v>48</v>
+      </c>
+      <c t="s" r="H216" s="4">
+        <v>49</v>
+      </c>
+      <c t="s" r="I216" s="4">
+        <v>50</v>
+      </c>
+      <c t="s" r="J216" s="4">
+        <v>47</v>
+      </c>
+      <c t="s" r="K216" s="4">
+        <v>51</v>
+      </c>
+      <c t="s" r="L216" s="4">
+        <v>51</v>
+      </c>
+      <c r="M216" s="4"/>
+      <c t="s" r="N216" s="4">
+        <v>52</v>
+      </c>
+      <c r="O216" s="5"/>
+      <c r="P216" s="5"/>
+      <c r="Q216" s="6"/>
+      <c r="R216" s="7"/>
+      <c r="S216" s="6"/>
+      <c r="T216" s="6"/>
+      <c r="U216" s="6"/>
+      <c r="V216" s="6"/>
+      <c r="W216" s="6"/>
+      <c r="X216" s="8"/>
+      <c r="Y216" s="6"/>
+      <c r="Z216" s="6"/>
+      <c r="AA216" s="8"/>
+      <c r="AB216" s="8"/>
+      <c r="AC216" s="8"/>
+      <c r="AD216" s="8"/>
+      <c r="AE216" s="6"/>
+      <c r="AF216" s="9"/>
+      <c r="AG216" s="5"/>
+      <c r="AH216" s="10"/>
+      <c r="AI216" s="11"/>
+      <c r="AJ216" s="12"/>
+      <c t="s" r="AK216" s="4">
+        <v>52</v>
+      </c>
+      <c t="s" r="AL216" s="4">
+        <v>52</v>
+      </c>
+      <c r="AM216" s="2">
+        <v>1</v>
+      </c>
+      <c r="AN216" s="2">
+        <v>1</v>
+      </c>
+      <c t="s" r="AO216" s="4">
+        <v>53</v>
+      </c>
+      <c t="s" r="AP216" s="4">
+        <v>54</v>
+      </c>
+      <c t="s" r="AQ216" s="4">
+        <v>55</v>
+      </c>
+      <c t="s" r="AR216" s="4">
         <v>300</v>
       </c>
-      <c t="s" r="B216" s="14">
+      <c t="s" r="AS216" s="4">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="217" ht="24.75" customHeight="1">
+      <c t="s" r="A217" s="14">
         <v>301</v>
       </c>
-      <c r="C216" s="15"/>
-      <c r="D216" s="15"/>
-      <c r="E216" s="15"/>
-      <c r="F216" s="15"/>
-      <c r="G216" s="15"/>
-      <c r="H216" s="15"/>
-      <c r="I216" s="15"/>
-      <c r="J216" s="15"/>
-      <c r="K216" s="15"/>
-      <c r="L216" s="15"/>
-      <c r="M216" s="15"/>
-      <c t="s" r="N216" s="15">
-        <v>52</v>
-      </c>
-      <c t="s" r="O216" s="14">
+      <c t="s" r="B217" s="14">
         <v>302</v>
       </c>
-      <c t="s" r="P216" s="14">
+      <c r="C217" s="15"/>
+      <c r="D217" s="15"/>
+      <c r="E217" s="15"/>
+      <c r="F217" s="15"/>
+      <c r="G217" s="15"/>
+      <c r="H217" s="15"/>
+      <c r="I217" s="15"/>
+      <c r="J217" s="15"/>
+      <c r="K217" s="15"/>
+      <c r="L217" s="15"/>
+      <c r="M217" s="15"/>
+      <c t="s" r="N217" s="15">
+        <v>52</v>
+      </c>
+      <c t="s" r="O217" s="14">
         <v>303</v>
       </c>
-      <c t="s" r="Q216" s="14">
+      <c t="s" r="P217" s="14">
         <v>304</v>
       </c>
-      <c t="s" r="R216" s="14">
+      <c t="s" r="Q217" s="14">
         <v>305</v>
       </c>
-      <c t="s" r="S216" s="14">
+      <c t="s" r="R217" s="14">
         <v>306</v>
       </c>
-      <c t="s" r="T216" s="14">
+      <c t="s" r="S217" s="14">
         <v>307</v>
       </c>
-      <c t="s" r="U216" s="14">
+      <c t="s" r="T217" s="14">
         <v>308</v>
       </c>
-      <c t="s" r="V216" s="14">
+      <c t="s" r="U217" s="14">
         <v>309</v>
       </c>
-      <c t="s" r="W216" s="14">
+      <c t="s" r="V217" s="14">
         <v>310</v>
       </c>
-      <c t="s" r="X216" s="14">
+      <c t="s" r="W217" s="14">
         <v>311</v>
       </c>
-      <c t="s" r="Y216" s="14">
+      <c t="s" r="X217" s="14">
         <v>312</v>
       </c>
-      <c t="s" r="Z216" s="14">
+      <c t="s" r="Y217" s="14">
         <v>313</v>
       </c>
-      <c t="s" r="AA216" s="14">
+      <c t="s" r="Z217" s="14">
         <v>314</v>
       </c>
-      <c t="s" r="AB216" s="14">
+      <c t="s" r="AA217" s="14">
         <v>315</v>
       </c>
-      <c t="s" r="AC216" s="14">
+      <c t="s" r="AB217" s="14">
         <v>316</v>
       </c>
-      <c t="s" r="AD216" s="14">
+      <c t="s" r="AC217" s="14">
         <v>317</v>
       </c>
-      <c t="s" r="AE216" s="14">
+      <c t="s" r="AD217" s="14">
         <v>318</v>
       </c>
-      <c r="AF216" s="14"/>
-      <c t="s" r="AG216" s="14">
+      <c t="s" r="AE217" s="14">
         <v>319</v>
       </c>
-      <c t="s" r="AH216" s="14">
+      <c r="AF217" s="14"/>
+      <c t="s" r="AG217" s="14">
         <v>320</v>
       </c>
-      <c t="s" r="AI216" s="14">
+      <c t="s" r="AH217" s="14">
         <v>321</v>
       </c>
-      <c r="AJ216" s="15"/>
-      <c t="s" r="AK216" s="15">
-        <v>52</v>
-      </c>
-      <c t="s" r="AL216" s="15">
-        <v>52</v>
-      </c>
-      <c t="s" r="AM216" s="14">
+      <c t="s" r="AI217" s="14">
         <v>322</v>
       </c>
-      <c t="s" r="AN216" s="14">
-        <v>322</v>
-      </c>
-      <c r="AO216" s="15"/>
-      <c r="AP216" s="15"/>
-      <c r="AQ216" s="15"/>
-      <c r="AR216" s="15"/>
-      <c r="AS216" s="15"/>
+      <c r="AJ217" s="15"/>
+      <c t="s" r="AK217" s="15">
+        <v>52</v>
+      </c>
+      <c t="s" r="AL217" s="15">
+        <v>52</v>
+      </c>
+      <c t="s" r="AM217" s="14">
+        <v>323</v>
+      </c>
+      <c t="s" r="AN217" s="14">
+        <v>323</v>
+      </c>
+      <c r="AO217" s="15"/>
+      <c r="AP217" s="15"/>
+      <c r="AQ217" s="15"/>
+      <c r="AR217" s="15"/>
+      <c r="AS217" s="15"/>
     </row>
   </sheetData>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:AS216" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:AS217" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-06).xlsx
+++ b/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-06).xlsx
@@ -915,24 +915,24 @@
   </si>
   <si>
     <t>215
-172</t>
-  </si>
-  <si>
-    <t>29</t>
-  </si>
-  <si>
-    <t>R$ 953.021,83</t>
-  </si>
-  <si>
-    <t>R$ 5.123,77
-R$ 5.275,77</t>
-  </si>
-  <si>
-    <t>(8.5%)
-(5.8%)</t>
-  </si>
-  <si>
-    <t>54.5</t>
+173</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>R$ 958.919,26</t>
+  </si>
+  <si>
+    <t>R$ 5.127,91
+R$ 5.279,37</t>
+  </si>
+  <si>
+    <t>(8.8%)
+(6.1%)</t>
+  </si>
+  <si>
+    <t>54.6</t>
   </si>
   <si>
     <t>(11.8%)</t>
@@ -941,7 +941,7 @@
     <t>35.0%</t>
   </si>
   <si>
-    <t>(19.9%)</t>
+    <t>(19.8%)</t>
   </si>
   <si>
     <t>3.5%</t>
@@ -950,19 +950,19 @@
     <t>0.5%</t>
   </si>
   <si>
-    <t>27.4</t>
-  </si>
-  <si>
-    <t>75.0%</t>
-  </si>
-  <si>
-    <t>10.2%</t>
+    <t>27.5</t>
+  </si>
+  <si>
+    <t>74.8%</t>
+  </si>
+  <si>
+    <t>10.3%</t>
   </si>
   <si>
     <t>5.6</t>
   </si>
   <si>
-    <t>6.9</t>
+    <t>7.0</t>
   </si>
   <si>
     <t>12.7</t>
@@ -971,10 +971,10 @@
     <t>19.2</t>
   </si>
   <si>
-    <t>71.7%</t>
-  </si>
-  <si>
-    <t>-R$ 26.308,52</t>
+    <t>71.6%</t>
+  </si>
+  <si>
+    <t>-R$ 26.364,32</t>
   </si>
   <si>
     <t>2.94</t>
@@ -11111,7 +11111,7 @@
         <v>-99.400000000000006</v>
       </c>
       <c r="AH76" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AI76" s="11"/>
       <c r="AJ76" s="13">
@@ -16583,7 +16583,7 @@
         <v>0</v>
       </c>
       <c r="AH120" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI120" s="11"/>
       <c r="AJ120" s="13">
@@ -21442,7 +21442,7 @@
         <v>19863</v>
       </c>
       <c r="B159" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C159" s="4">
         <v>44</v>
@@ -21478,27 +21478,61 @@
       <c t="s" r="N159" s="4">
         <v>52</v>
       </c>
-      <c r="O159" s="5"/>
-      <c r="P159" s="5"/>
-      <c r="Q159" s="6"/>
-      <c r="R159" s="7"/>
-      <c r="S159" s="6"/>
-      <c r="T159" s="6"/>
-      <c r="U159" s="6"/>
-      <c r="V159" s="6"/>
-      <c r="W159" s="6"/>
-      <c r="X159" s="8"/>
-      <c r="Y159" s="6"/>
-      <c r="Z159" s="6"/>
-      <c r="AA159" s="8"/>
-      <c r="AB159" s="8"/>
+      <c r="O159" s="5">
+        <v>5897.4300000000003</v>
+      </c>
+      <c r="P159" s="5">
+        <v>5897.4300000000003</v>
+      </c>
+      <c r="Q159" s="6">
+        <v>-0.39030850394042671</v>
+      </c>
+      <c r="R159" s="7">
+        <v>75</v>
+      </c>
+      <c r="S159" s="6">
+        <v>-0.0625</v>
+      </c>
+      <c r="T159" s="6">
+        <v>0.27688920428050862</v>
+      </c>
+      <c r="U159" s="6">
+        <v>-0.016048566918132137</v>
+      </c>
+      <c r="V159" s="6">
+        <v>0.043166514905645333</v>
+      </c>
+      <c r="W159" s="6">
+        <v>0.0080732624210885073</v>
+      </c>
+      <c r="X159" s="8">
+        <v>31.801482222222223</v>
+      </c>
+      <c r="Y159" s="6">
+        <v>0.48888888888888887</v>
+      </c>
+      <c r="Z159" s="6">
+        <v>0.20000000000000001</v>
+      </c>
+      <c r="AA159" s="8">
+        <v>5.0100523809523816</v>
+      </c>
+      <c r="AB159" s="8">
+        <v>8.7056818181818176</v>
+      </c>
       <c r="AC159" s="8">
         <v>14.189755</v>
       </c>
-      <c r="AD159" s="8"/>
-      <c r="AE159" s="6"/>
+      <c r="AD159" s="8">
+        <v>20.787406666666666</v>
+      </c>
+      <c r="AE159" s="6">
+        <v>0.59999999999999998</v>
+      </c>
       <c r="AF159" s="9"/>
-      <c r="AG159" s="5"/>
+      <c r="AG159" s="5">
+        <v>-55.799999999999997</v>
+      </c>
       <c r="AH159" s="10">
         <v>2</v>
       </c>

--- a/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-06).xlsx
+++ b/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-06).xlsx
@@ -915,51 +915,51 @@
   </si>
   <si>
     <t>215
-173</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>R$ 958.919,26</t>
-  </si>
-  <si>
-    <t>R$ 5.127,91
-R$ 5.279,37</t>
-  </si>
-  <si>
-    <t>(8.8%)
-(6.1%)</t>
+174</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>R$ 964.871,95</t>
+  </si>
+  <si>
+    <t>R$ 5.132,30
+R$ 5.283,24</t>
+  </si>
+  <si>
+    <t>(8.9%)
+(6.2%)</t>
   </si>
   <si>
     <t>54.6</t>
   </si>
   <si>
-    <t>(11.8%)</t>
-  </si>
-  <si>
-    <t>35.0%</t>
-  </si>
-  <si>
-    <t>(19.8%)</t>
+    <t>(11.9%)</t>
+  </si>
+  <si>
+    <t>40.0%</t>
+  </si>
+  <si>
+    <t>(14.7%)</t>
   </si>
   <si>
     <t>3.5%</t>
   </si>
   <si>
-    <t>0.5%</t>
+    <t>0.6%</t>
   </si>
   <si>
     <t>27.5</t>
   </si>
   <si>
-    <t>74.8%</t>
-  </si>
-  <si>
-    <t>10.3%</t>
-  </si>
-  <si>
-    <t>5.6</t>
+    <t>74.9%</t>
+  </si>
+  <si>
+    <t>10.5%</t>
+  </si>
+  <si>
+    <t>5.7</t>
   </si>
   <si>
     <t>7.0</t>
@@ -968,13 +968,13 @@
     <t>12.7</t>
   </si>
   <si>
-    <t>19.2</t>
-  </si>
-  <si>
-    <t>71.6%</t>
-  </si>
-  <si>
-    <t>-R$ 26.364,32</t>
+    <t>19.3</t>
+  </si>
+  <si>
+    <t>71.5%</t>
+  </si>
+  <si>
+    <t>-R$ 26.470,22</t>
   </si>
   <si>
     <t>2.94</t>
@@ -4876,7 +4876,7 @@
         <v>-333</v>
       </c>
       <c r="AH27" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI27" s="11"/>
       <c r="AJ27" s="13">
@@ -12674,7 +12674,7 @@
         <v>19693</v>
       </c>
       <c r="B89" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C89" s="4">
         <v>44</v>
@@ -12708,25 +12708,59 @@
       <c t="s" r="N89" s="4">
         <v>52</v>
       </c>
-      <c r="O89" s="5"/>
-      <c r="P89" s="5"/>
-      <c r="Q89" s="6"/>
-      <c r="R89" s="7"/>
-      <c r="S89" s="6"/>
-      <c r="T89" s="6"/>
-      <c r="U89" s="6"/>
-      <c r="V89" s="6"/>
-      <c r="W89" s="6"/>
-      <c r="X89" s="8"/>
-      <c r="Y89" s="6"/>
-      <c r="Z89" s="6"/>
-      <c r="AA89" s="8"/>
-      <c r="AB89" s="8"/>
+      <c r="O89" s="5">
+        <v>5952.6899999999996</v>
+      </c>
+      <c r="P89" s="5">
+        <v>5952.6899999999996</v>
+      </c>
+      <c r="Q89" s="6">
+        <v>-0.15670421769015874</v>
+      </c>
+      <c r="R89" s="7">
+        <v>56</v>
+      </c>
+      <c r="S89" s="6">
+        <v>-0.2432432432432432</v>
+      </c>
+      <c r="T89" s="6">
+        <v>8.3839883145267109</v>
+      </c>
+      <c r="U89" s="6">
+        <v>8.0041768343387609</v>
+      </c>
+      <c r="V89" s="6">
+        <v>0.03328856365777489</v>
+      </c>
+      <c r="W89" s="6">
+        <v>0.015740194769087591</v>
+      </c>
+      <c r="X89" s="8">
+        <v>42.343335000000003</v>
+      </c>
+      <c r="Y89" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z89" s="6">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="AA89" s="8">
+        <v>12.360819298245614</v>
+      </c>
+      <c r="AB89" s="8">
+        <v>13.717500000000001</v>
+      </c>
       <c r="AC89" s="8"/>
-      <c r="AD89" s="8"/>
-      <c r="AE89" s="6"/>
+      <c r="AD89" s="8">
+        <v>34.279164999999999</v>
+      </c>
+      <c r="AE89" s="6">
+        <v>0.29999999999999999</v>
+      </c>
       <c r="AF89" s="9"/>
-      <c r="AG89" s="5"/>
+      <c r="AG89" s="5">
+        <v>-105.90000000000001</v>
+      </c>
       <c r="AH89" s="10">
         <v>2</v>
       </c>
@@ -14256,7 +14290,7 @@
         <v>0</v>
       </c>
       <c r="AH101" s="10">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AI101" s="11"/>
       <c r="AJ101" s="13">
@@ -24792,7 +24826,7 @@
         <v>19923</v>
       </c>
       <c r="B185" s="3">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c t="s" r="C185" s="4">
         <v>44</v>
@@ -25763,7 +25797,7 @@
         <v>0</v>
       </c>
       <c r="AH192" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI192" s="11"/>
       <c r="AJ192" s="13">
@@ -27074,7 +27108,7 @@
         <v>19957</v>
       </c>
       <c r="B203" s="3">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c t="s" r="C203" s="4">
         <v>44</v>
@@ -28483,7 +28517,7 @@
         <v>19980</v>
       </c>
       <c r="B216" s="3">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c t="s" r="C216" s="4">
         <v>44</v>

--- a/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-06).xlsx
+++ b/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-06).xlsx
@@ -915,39 +915,39 @@
   </si>
   <si>
     <t>215
-174</t>
-  </si>
-  <si>
-    <t>27</t>
-  </si>
-  <si>
-    <t>R$ 964.871,95</t>
-  </si>
-  <si>
-    <t>R$ 5.132,30
-R$ 5.283,24</t>
-  </si>
-  <si>
-    <t>(8.9%)
-(6.2%)</t>
-  </si>
-  <si>
-    <t>54.6</t>
+179</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>R$ 974.723,24</t>
+  </si>
+  <si>
+    <t>R$ 5.050,38
+R$ 5.190,70</t>
+  </si>
+  <si>
+    <t>(9.0%)
+(6.4%)</t>
+  </si>
+  <si>
+    <t>53.8</t>
   </si>
   <si>
     <t>(11.9%)</t>
   </si>
   <si>
-    <t>40.0%</t>
-  </si>
-  <si>
-    <t>(14.7%)</t>
+    <t>39.9%</t>
+  </si>
+  <si>
+    <t>(14.6%)</t>
   </si>
   <si>
     <t>3.5%</t>
   </si>
   <si>
-    <t>0.6%</t>
+    <t>0.5%</t>
   </si>
   <si>
     <t>27.5</t>
@@ -956,25 +956,25 @@
     <t>74.9%</t>
   </si>
   <si>
-    <t>10.5%</t>
+    <t>10.4%</t>
   </si>
   <si>
     <t>5.7</t>
   </si>
   <si>
-    <t>7.0</t>
-  </si>
-  <si>
-    <t>12.7</t>
-  </si>
-  <si>
-    <t>19.3</t>
-  </si>
-  <si>
-    <t>71.5%</t>
-  </si>
-  <si>
-    <t>-R$ 26.470,22</t>
+    <t>6.9</t>
+  </si>
+  <si>
+    <t>12.6</t>
+  </si>
+  <si>
+    <t>19.2</t>
+  </si>
+  <si>
+    <t>71.6%</t>
+  </si>
+  <si>
+    <t>-R$ 26.322,22</t>
   </si>
   <si>
     <t>2.94</t>
@@ -7920,7 +7920,7 @@
         <v>19602</v>
       </c>
       <c r="B51" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C51" s="4">
         <v>44</v>
@@ -7956,25 +7956,59 @@
       <c t="s" r="N51" s="4">
         <v>52</v>
       </c>
-      <c r="O51" s="5"/>
-      <c r="P51" s="5"/>
-      <c r="Q51" s="6"/>
-      <c r="R51" s="7"/>
-      <c r="S51" s="6"/>
-      <c r="T51" s="6"/>
-      <c r="U51" s="6"/>
-      <c r="V51" s="6"/>
-      <c r="W51" s="6"/>
-      <c r="X51" s="8"/>
-      <c r="Y51" s="6"/>
-      <c r="Z51" s="6"/>
-      <c r="AA51" s="8"/>
-      <c r="AB51" s="8"/>
+      <c r="O51" s="5">
+        <v>769.70000000000005</v>
+      </c>
+      <c r="P51" s="5">
+        <v>769.70000000000005</v>
+      </c>
+      <c r="Q51" s="6">
+        <v>-0.14411208717891688</v>
+      </c>
+      <c r="R51" s="7">
+        <v>9</v>
+      </c>
+      <c r="S51" s="6">
+        <v>0</v>
+      </c>
+      <c r="T51" s="6">
+        <v>0</v>
+      </c>
+      <c r="U51" s="6">
+        <v>-0.38912563336364814</v>
+      </c>
+      <c r="V51" s="6">
+        <v>0.063977523710536569</v>
+      </c>
+      <c r="W51" s="6">
+        <v>-0.10233402624399116</v>
+      </c>
+      <c r="X51" s="8">
+        <v>27.274999999999999</v>
+      </c>
+      <c r="Y51" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z51" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="AA51" s="8">
+        <v>3.1111111111111112</v>
+      </c>
+      <c r="AB51" s="8">
+        <v>15.85</v>
+      </c>
       <c r="AC51" s="8"/>
-      <c r="AD51" s="8"/>
-      <c r="AE51" s="6"/>
+      <c r="AD51" s="8">
+        <v>14.75835</v>
+      </c>
+      <c r="AE51" s="6">
+        <v>0.5</v>
+      </c>
       <c r="AF51" s="9"/>
-      <c r="AG51" s="5"/>
+      <c r="AG51" s="5">
+        <v>0</v>
+      </c>
       <c r="AH51" s="10">
         <v>2</v>
       </c>
@@ -8847,7 +8881,9 @@
       <c r="Z58" s="6"/>
       <c r="AA58" s="8"/>
       <c r="AB58" s="8"/>
-      <c r="AC58" s="8"/>
+      <c r="AC58" s="8">
+        <v>8.8918289999999995</v>
+      </c>
       <c r="AD58" s="8"/>
       <c r="AE58" s="6"/>
       <c r="AF58" s="9"/>
@@ -20536,7 +20572,7 @@
         <v>19821</v>
       </c>
       <c r="B151" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C151" s="4">
         <v>44</v>
@@ -20572,25 +20608,61 @@
       <c t="s" r="N151" s="4">
         <v>52</v>
       </c>
-      <c r="O151" s="5"/>
-      <c r="P151" s="5"/>
-      <c r="Q151" s="6"/>
-      <c r="R151" s="7"/>
-      <c r="S151" s="6"/>
-      <c r="T151" s="6"/>
-      <c r="U151" s="6"/>
-      <c r="V151" s="6"/>
-      <c r="W151" s="6"/>
-      <c r="X151" s="8"/>
-      <c r="Y151" s="6"/>
-      <c r="Z151" s="6"/>
-      <c r="AA151" s="8"/>
-      <c r="AB151" s="8"/>
-      <c r="AC151" s="8"/>
-      <c r="AD151" s="8"/>
-      <c r="AE151" s="6"/>
+      <c r="O151" s="5">
+        <v>2257.04</v>
+      </c>
+      <c r="P151" s="5">
+        <v>2257.04</v>
+      </c>
+      <c r="Q151" s="6">
+        <v>-0.090270052398226497</v>
+      </c>
+      <c r="R151" s="7">
+        <v>33</v>
+      </c>
+      <c r="S151" s="6">
+        <v>0.22222222222222232</v>
+      </c>
+      <c r="T151" s="6">
+        <v>0.29445876014603195</v>
+      </c>
+      <c r="U151" s="6">
+        <v>-0.059589019246446676</v>
+      </c>
+      <c r="V151" s="6">
+        <v>0.039432619714316101</v>
+      </c>
+      <c r="W151" s="6">
+        <v>-0.016095860064509269</v>
+      </c>
+      <c r="X151" s="8">
+        <v>24.042307692307695</v>
+      </c>
+      <c r="Y151" s="6">
+        <v>0.69230769230769229</v>
+      </c>
+      <c r="Z151" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA151" s="8">
+        <v>3.8411468750000002</v>
+      </c>
+      <c r="AB151" s="8">
+        <v>2.4910269230769231</v>
+      </c>
+      <c r="AC151" s="8">
+        <v>6.5150240000000004</v>
+      </c>
+      <c r="AD151" s="8">
+        <v>13.364103846153846</v>
+      </c>
+      <c r="AE151" s="6">
+        <v>0.84615384615384615</v>
+      </c>
       <c r="AF151" s="9"/>
-      <c r="AG151" s="5"/>
+      <c r="AG151" s="5">
+        <v>0</v>
+      </c>
       <c r="AH151" s="10">
         <v>5</v>
       </c>
@@ -21286,7 +21358,7 @@
         <v>19855</v>
       </c>
       <c r="B157" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C157" s="4">
         <v>44</v>
@@ -21322,25 +21394,61 @@
       <c t="s" r="N157" s="4">
         <v>52</v>
       </c>
-      <c r="O157" s="5"/>
-      <c r="P157" s="5"/>
-      <c r="Q157" s="6"/>
-      <c r="R157" s="7"/>
-      <c r="S157" s="6"/>
-      <c r="T157" s="6"/>
-      <c r="U157" s="6"/>
-      <c r="V157" s="6"/>
-      <c r="W157" s="6"/>
-      <c r="X157" s="8"/>
-      <c r="Y157" s="6"/>
-      <c r="Z157" s="6"/>
-      <c r="AA157" s="8"/>
-      <c r="AB157" s="8"/>
-      <c r="AC157" s="8"/>
-      <c r="AD157" s="8"/>
-      <c r="AE157" s="6"/>
+      <c r="O157" s="5">
+        <v>2398.7600000000002</v>
+      </c>
+      <c r="P157" s="5">
+        <v>2398.7600000000002</v>
+      </c>
+      <c r="Q157" s="6">
+        <v>0.23068240702262033</v>
+      </c>
+      <c r="R157" s="7">
+        <v>26</v>
+      </c>
+      <c r="S157" s="6">
+        <v>0.040000000000000036</v>
+      </c>
+      <c r="T157" s="6">
+        <v>0.36979664493321546</v>
+      </c>
+      <c r="U157" s="6">
+        <v>-0.0040381697210225284</v>
+      </c>
+      <c r="V157" s="6">
+        <v>0.072519343327385813</v>
+      </c>
+      <c r="W157" s="6">
+        <v>0.032361094899031162</v>
+      </c>
+      <c r="X157" s="8">
+        <v>26.847500000000004</v>
+      </c>
+      <c r="Y157" s="6">
+        <v>0.80000000000000004</v>
+      </c>
+      <c r="Z157" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA157" s="8">
+        <v>6.2925925925925927</v>
+      </c>
+      <c r="AB157" s="8">
+        <v>3.271665</v>
+      </c>
+      <c r="AC157" s="8">
+        <v>9.8741660000000007</v>
+      </c>
+      <c r="AD157" s="8">
+        <v>16.82</v>
+      </c>
+      <c r="AE157" s="6">
+        <v>0.84999999999999998</v>
+      </c>
       <c r="AF157" s="9"/>
-      <c r="AG157" s="5"/>
+      <c r="AG157" s="5">
+        <v>0</v>
+      </c>
       <c r="AH157" s="10">
         <v>4</v>
       </c>
@@ -21381,7 +21489,7 @@
         <v>19859</v>
       </c>
       <c r="B158" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C158" s="4">
         <v>44</v>
@@ -21417,25 +21525,61 @@
       <c t="s" r="N158" s="4">
         <v>52</v>
       </c>
-      <c r="O158" s="5"/>
-      <c r="P158" s="5"/>
-      <c r="Q158" s="6"/>
-      <c r="R158" s="7"/>
-      <c r="S158" s="6"/>
-      <c r="T158" s="6"/>
-      <c r="U158" s="6"/>
-      <c r="V158" s="6"/>
-      <c r="W158" s="6"/>
-      <c r="X158" s="8"/>
-      <c r="Y158" s="6"/>
-      <c r="Z158" s="6"/>
-      <c r="AA158" s="8"/>
-      <c r="AB158" s="8"/>
-      <c r="AC158" s="8"/>
-      <c r="AD158" s="8"/>
-      <c r="AE158" s="6"/>
+      <c r="O158" s="5">
+        <v>2082.6900000000001</v>
+      </c>
+      <c r="P158" s="5">
+        <v>2082.6900000000001</v>
+      </c>
+      <c r="Q158" s="6">
+        <v>-0.37501988050690038</v>
+      </c>
+      <c r="R158" s="7">
+        <v>23</v>
+      </c>
+      <c r="S158" s="6">
+        <v>-0.34285714285714286</v>
+      </c>
+      <c r="T158" s="6">
+        <v>0.30115273996610153</v>
+      </c>
+      <c r="U158" s="6">
+        <v>0.010864699019057084</v>
+      </c>
+      <c r="V158" s="6">
+        <v>0.054470900614109634</v>
+      </c>
+      <c r="W158" s="6">
+        <v>-0.0018889032933369825</v>
+      </c>
+      <c r="X158" s="8">
+        <v>30.580700000000004</v>
+      </c>
+      <c r="Y158" s="6">
+        <v>0.57894736842105265</v>
+      </c>
+      <c r="Z158" s="6">
+        <v>0.21052631578947367</v>
+      </c>
+      <c r="AA158" s="8">
+        <v>6.8969681818181821</v>
+      </c>
+      <c r="AB158" s="8">
+        <v>2.8096473684210523</v>
+      </c>
+      <c r="AC158" s="8">
+        <v>10.145613000000001</v>
+      </c>
+      <c r="AD158" s="8">
+        <v>17.068421052631578</v>
+      </c>
+      <c r="AE158" s="6">
+        <v>0.63157894736842102</v>
+      </c>
       <c r="AF158" s="9"/>
-      <c r="AG158" s="5"/>
+      <c r="AG158" s="5">
+        <v>0</v>
+      </c>
       <c r="AH158" s="10">
         <v>2</v>
       </c>
@@ -22252,7 +22396,7 @@
         <v>19877</v>
       </c>
       <c r="B165" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C165" s="4">
         <v>44</v>
@@ -22288,25 +22432,61 @@
       <c t="s" r="N165" s="4">
         <v>52</v>
       </c>
-      <c r="O165" s="5"/>
-      <c r="P165" s="5"/>
-      <c r="Q165" s="6"/>
-      <c r="R165" s="7"/>
-      <c r="S165" s="6"/>
-      <c r="T165" s="6"/>
-      <c r="U165" s="6"/>
-      <c r="V165" s="6"/>
-      <c r="W165" s="6"/>
-      <c r="X165" s="8"/>
-      <c r="Y165" s="6"/>
-      <c r="Z165" s="6"/>
-      <c r="AA165" s="8"/>
-      <c r="AB165" s="8"/>
-      <c r="AC165" s="8"/>
-      <c r="AD165" s="8"/>
-      <c r="AE165" s="6"/>
+      <c r="O165" s="5">
+        <v>2343.0999999999999</v>
+      </c>
+      <c r="P165" s="5">
+        <v>2343.0999999999999</v>
+      </c>
+      <c r="Q165" s="6">
+        <v>-0.47710332515063603</v>
+      </c>
+      <c r="R165" s="7">
+        <v>27</v>
+      </c>
+      <c r="S165" s="6">
+        <v>-0.51785714285714279</v>
+      </c>
+      <c r="T165" s="6">
+        <v>0.35004937902778371</v>
+      </c>
+      <c r="U165" s="6">
+        <v>-0.0016598950108830182</v>
+      </c>
+      <c r="V165" s="6">
+        <v>0.03959178012035338</v>
+      </c>
+      <c r="W165" s="6">
+        <v>-0.017349878366266912</v>
+      </c>
+      <c r="X165" s="8">
+        <v>20.638235294117649</v>
+      </c>
+      <c r="Y165" s="6">
+        <v>0.76470588235294112</v>
+      </c>
+      <c r="Z165" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA165" s="8">
+        <v>4.3746925925925924</v>
+      </c>
+      <c r="AB165" s="8">
+        <v>3.5725470588235293</v>
+      </c>
+      <c r="AC165" s="8">
+        <v>8.0873629999999999</v>
+      </c>
+      <c r="AD165" s="8">
+        <v>14.901958823529412</v>
+      </c>
+      <c r="AE165" s="6">
+        <v>1</v>
+      </c>
       <c r="AF165" s="9"/>
-      <c r="AG165" s="5"/>
+      <c r="AG165" s="5">
+        <v>148</v>
+      </c>
       <c r="AH165" s="10">
         <v>3</v>
       </c>
